--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110096</v>
+        <v>110098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99381</v>
+        <v>99383</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99384</v>
+        <v>99390</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99390</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136773838</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136773853</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136773854</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136773855</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136773856</v>
       </c>
       <c r="B17" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>136773857</v>
       </c>
       <c r="B18" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>136773859</v>
       </c>
       <c r="B19" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136773860</v>
       </c>
       <c r="B20" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>136773861</v>
       </c>
       <c r="B21" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>136773865</v>
       </c>
       <c r="B22" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136773866</v>
       </c>
       <c r="B23" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136773867</v>
       </c>
       <c r="B24" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>136773868</v>
       </c>
       <c r="B25" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136773869</v>
       </c>
       <c r="B26" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>136773870</v>
       </c>
       <c r="B27" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136773872</v>
       </c>
       <c r="B28" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>136773839</v>
       </c>
       <c r="B29" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136773864</v>
       </c>
       <c r="B30" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99398</v>
+        <v>99411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136773838</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136773853</v>
       </c>
       <c r="B14" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>136773854</v>
       </c>
       <c r="B15" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>136773855</v>
       </c>
       <c r="B16" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>136773856</v>
       </c>
       <c r="B17" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>136773857</v>
       </c>
       <c r="B18" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>136773859</v>
       </c>
       <c r="B19" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136773860</v>
       </c>
       <c r="B20" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>136773861</v>
       </c>
       <c r="B21" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>136773865</v>
       </c>
       <c r="B22" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>136773866</v>
       </c>
       <c r="B23" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136773867</v>
       </c>
       <c r="B24" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>136773868</v>
       </c>
       <c r="B25" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136773869</v>
       </c>
       <c r="B26" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>136773870</v>
       </c>
       <c r="B27" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136773872</v>
       </c>
       <c r="B28" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>136773839</v>
       </c>
       <c r="B29" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136773864</v>
       </c>
       <c r="B30" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136773862</v>
       </c>
       <c r="B31" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>136773863</v>
       </c>
       <c r="B32" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -1941,11 +1941,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2058,11 +2054,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2175,11 +2167,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2292,11 +2280,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2409,11 +2393,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2526,11 +2506,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2643,11 +2619,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2760,11 +2732,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2877,11 +2845,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -2994,11 +2958,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3111,11 +3071,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3228,11 +3184,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3345,11 +3297,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3462,11 +3410,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3579,11 +3523,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3696,11 +3636,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3813,11 +3749,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -3934,11 +3866,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -4051,11 +3979,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>
@@ -4168,11 +4092,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Granbergsvilan, Dlr</t>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -4179,7 +4179,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99413</v>
+        <v>99416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136773838</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136773853</v>
       </c>
       <c r="B14" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136773854</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>136773855</v>
       </c>
       <c r="B16" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136773856</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136773857</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136773859</v>
       </c>
       <c r="B19" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>136773860</v>
       </c>
       <c r="B20" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136773861</v>
       </c>
       <c r="B21" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136773865</v>
       </c>
       <c r="B22" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136773866</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>136773867</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>136773868</v>
       </c>
       <c r="B25" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136773869</v>
       </c>
       <c r="B26" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136773870</v>
       </c>
       <c r="B27" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136773872</v>
       </c>
       <c r="B28" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>136773839</v>
       </c>
       <c r="B29" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>136773864</v>
       </c>
       <c r="B30" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>136773862</v>
       </c>
       <c r="B31" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>136773863</v>
       </c>
       <c r="B32" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99416</v>
+        <v>99426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -4179,7 +4179,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99426</v>
+        <v>99427</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136773848</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136773831</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136773834</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136773835</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136773840</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136773841</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136773846</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136773847</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136773850</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136773852</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136773873</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136773838</v>
       </c>
       <c r="B13" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>136773853</v>
       </c>
       <c r="B14" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136773854</v>
       </c>
       <c r="B15" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>136773855</v>
       </c>
       <c r="B16" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136773856</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136773857</v>
       </c>
       <c r="B18" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136773859</v>
       </c>
       <c r="B19" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>136773860</v>
       </c>
       <c r="B20" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136773861</v>
       </c>
       <c r="B21" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136773865</v>
       </c>
       <c r="B22" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136773866</v>
       </c>
       <c r="B23" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>136773867</v>
       </c>
       <c r="B24" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>136773868</v>
       </c>
       <c r="B25" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136773869</v>
       </c>
       <c r="B26" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136773870</v>
       </c>
       <c r="B27" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136773872</v>
       </c>
       <c r="B28" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>136773839</v>
       </c>
       <c r="B29" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>136773864</v>
       </c>
       <c r="B30" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110163</v>
+        <v>110168</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99427</v>
+        <v>99432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37289-2026 artfynd.xlsx
+++ b/artfynd/A 37289-2026 artfynd.xlsx
@@ -4179,7 +4179,7 @@
         <v>136773874</v>
       </c>
       <c r="B33" t="n">
-        <v>110168</v>
+        <v>110171</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136773832</v>
       </c>
       <c r="B34" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136773837</v>
       </c>
       <c r="B35" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>136773851</v>
       </c>
       <c r="B36" t="n">
-        <v>99432</v>
+        <v>99434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
